--- a/data/trans_orig/P72-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P72-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el intervalo en el que están comprendidos los ingresos totales netos de su hogar en 2007</t>
+          <t>Población según el intervalo en el que están comprendidos los ingresos totales netos de su hogar en 2007 (tasa de respuesta: 53,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,62 +767,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5234</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>909</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4188</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>9886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>12170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19567</t>
+          <t>19685</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29170</t>
+          <t>30964</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29668</t>
+          <t>30856</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55368</t>
+          <t>56370</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27469</t>
+          <t>26971</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51217</t>
+          <t>51497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62999</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96611</t>
+          <t>98606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109400</t>
+          <t>108263</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149788</t>
+          <t>149485</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84333</t>
+          <t>84642</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>120724</t>
+          <t>122403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205427</t>
+          <t>203922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>262259</t>
+          <t>261295</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>170091</t>
+          <t>170401</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>215506</t>
+          <t>215112</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>206147</t>
+          <t>206190</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>256623</t>
+          <t>254526</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>387455</t>
+          <t>388332</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>458402</t>
+          <t>457918</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>188727</t>
+          <t>188274</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>234243</t>
+          <t>234098</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1445,12 +1445,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>221689</t>
+          <t>226380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>274087</t>
+          <t>277170</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>425044</t>
+          <t>427084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>494683</t>
+          <t>494219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>32514</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55726</t>
+          <t>57527</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88826</t>
+          <t>89764</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77698</t>
+          <t>76776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116008</t>
+          <t>115809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10173</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14018</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33632</t>
+          <t>35123</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21603</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26301</t>
+          <t>25316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50466</t>
+          <t>49017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>25617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49958</t>
+          <t>51046</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23015</t>
+          <t>23734</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48242</t>
+          <t>46363</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>55612</t>
+          <t>55129</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>88724</t>
+          <t>87216</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115224</t>
+          <t>113564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160285</t>
+          <t>157670</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110881</t>
+          <t>110923</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151969</t>
+          <t>153826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>240357</t>
+          <t>239230</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298987</t>
+          <t>299834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>270417</t>
+          <t>267340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>327053</t>
+          <t>322940</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195710</t>
+          <t>192444</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>247490</t>
+          <t>242832</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>477019</t>
+          <t>475150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>551954</t>
+          <t>552583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>282415</t>
+          <t>283792</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>342493</t>
+          <t>343961</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>265093</t>
+          <t>264631</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>321462</t>
+          <t>319659</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>562452</t>
+          <t>563350</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>643357</t>
+          <t>647515</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2431,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72733</t>
+          <t>74923</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112164</t>
+          <t>112999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79399</t>
+          <t>81065</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117768</t>
+          <t>119155</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>164583</t>
+          <t>165559</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>218614</t>
+          <t>220992</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20021</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>19956</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13810</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33254</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15170</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25721</t>
+          <t>25659</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48513</t>
+          <t>50591</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>28085</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41037</t>
+          <t>40865</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70485</t>
+          <t>68978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30073</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53966</t>
+          <t>53361</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27314</t>
+          <t>26302</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49500</t>
+          <t>49136</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>63468</t>
+          <t>60987</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97138</t>
+          <t>94737</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67444</t>
+          <t>68603</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99738</t>
+          <t>101186</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41568</t>
+          <t>42150</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68132</t>
+          <t>68185</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>116967</t>
+          <t>118834</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>158096</t>
+          <t>159764</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>63372</t>
+          <t>62022</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>97374</t>
+          <t>96820</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43126</t>
+          <t>42713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69538</t>
+          <t>68981</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>114190</t>
+          <t>117382</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>157003</t>
+          <t>157682</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,71%</t>
         </is>
       </c>
     </row>
@@ -3339,12 +3339,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>34122</t>
+          <t>35177</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>61214</t>
+          <t>60845</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38313</t>
+          <t>38425</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>64043</t>
+          <t>64194</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3409,12 +3409,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>79674</t>
+          <t>77330</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>118480</t>
+          <t>114592</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>14064</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>31754</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20666</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>42557</t>
+          <t>44671</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16967</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>14684</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,72 +3815,72 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>6162</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>13362</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>6162</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>2908</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>13288</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>12483</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>6230</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>22633</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>12483</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>6485</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>22480</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>47579</t>
+          <t>47532</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>78855</t>
+          <t>79742</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22495</t>
+          <t>22620</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45248</t>
+          <t>45512</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>78025</t>
+          <t>78620</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>118586</t>
+          <t>118330</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>69939</t>
+          <t>69105</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>105753</t>
+          <t>106374</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>66147</t>
+          <t>66244</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>99033</t>
+          <t>102050</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>145503</t>
+          <t>141215</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>196817</t>
+          <t>192482</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4134,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>232997</t>
+          <t>232917</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>296403</t>
+          <t>292820</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>197844</t>
+          <t>197610</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>253246</t>
+          <t>254528</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>442931</t>
+          <t>446559</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>527855</t>
+          <t>527007</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>466495</t>
+          <t>468217</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>541293</t>
+          <t>540572</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>344432</t>
+          <t>344610</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>408238</t>
+          <t>411741</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>825011</t>
+          <t>827912</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>931409</t>
+          <t>931243</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>516322</t>
+          <t>509644</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>593488</t>
+          <t>590979</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>528913</t>
+          <t>533264</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>610399</t>
+          <t>611559</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1069175</t>
+          <t>1072023</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1176846</t>
+          <t>1181565</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -4473,12 +4473,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>280896</t>
+          <t>284699</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>347679</t>
+          <t>348028</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>334732</t>
+          <t>331201</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>402904</t>
+          <t>404129</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>636480</t>
+          <t>631236</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>726579</t>
+          <t>727491</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>27253</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>54362</t>
+          <t>53281</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>72137</t>
+          <t>72400</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>108439</t>
+          <t>107768</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>106527</t>
+          <t>105098</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>151974</t>
+          <t>151543</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el intervalo en el que están comprendidos los ingresos totales netos de su hogar en 2012</t>
+          <t>Población según el intervalo en el que están comprendidos los ingresos totales netos de su hogar en 2012 (tasa de respuesta: 76,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5047,82 +5047,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2134</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6432</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2134</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8611</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2134</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29377</t>
+          <t>29733</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5421,12 +5421,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43922</t>
+          <t>43754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36298</t>
+          <t>35749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66534</t>
+          <t>65164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5499,12 +5499,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66209</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101758</t>
+          <t>103178</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77549</t>
+          <t>74860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117129</t>
+          <t>112754</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151503</t>
+          <t>151987</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204527</t>
+          <t>204493</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>269372</t>
+          <t>267818</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>325562</t>
+          <t>324377</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>358312</t>
+          <t>355228</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>423154</t>
+          <t>423972</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>645033</t>
+          <t>649383</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>732886</t>
+          <t>728769</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -5725,12 +5725,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>300573</t>
+          <t>299776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>356690</t>
+          <t>357067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>463268</t>
+          <t>466873</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>530230</t>
+          <t>530565</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>782442</t>
+          <t>781504</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>871471</t>
+          <t>868920</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46034</t>
+          <t>45507</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76510</t>
+          <t>76427</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5853,82 +5853,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>69644</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>54796</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>86528</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>129792</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>109385</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>153842</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>5,79%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69644</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>54076</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86397</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>129792</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>109266</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>154141</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15758</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38455</t>
+          <t>39590</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>22279</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46127</t>
+          <t>47708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -6294,12 +6294,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>37564</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>71014</t>
+          <t>66872</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>32068</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59775</t>
+          <t>59543</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6344,12 +6344,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>76653</t>
+          <t>77785</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119152</t>
+          <t>117799</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -6407,12 +6407,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>117688</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>164664</t>
+          <t>162237</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95409</t>
+          <t>95531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138064</t>
+          <t>138850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>224103</t>
+          <t>223562</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>286298</t>
+          <t>286950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>267970</t>
+          <t>269779</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>331794</t>
+          <t>333468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>245764</t>
+          <t>244112</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>307039</t>
+          <t>306401</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>533155</t>
+          <t>531713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>624091</t>
+          <t>618135</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561555</t>
+          <t>560059</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>636946</t>
+          <t>636333</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>491946</t>
+          <t>492125</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>561615</t>
+          <t>565075</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1074402</t>
+          <t>1076894</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1181230</t>
+          <t>1181240</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>252868</t>
+          <t>249764</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>312906</t>
+          <t>311842</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>277225</t>
+          <t>274280</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341459</t>
+          <t>340758</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>547041</t>
+          <t>543055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>635867</t>
+          <t>628899</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -6859,12 +6859,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47090</t>
+          <t>47417</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78493</t>
+          <t>80211</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41445</t>
+          <t>40143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71490</t>
+          <t>72585</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94023</t>
+          <t>92770</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>140148</t>
+          <t>140030</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -7202,12 +7202,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15388</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36748</t>
+          <t>35958</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32026</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31393</t>
+          <t>31834</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60969</t>
+          <t>59994</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -7315,12 +7315,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24742</t>
+          <t>23818</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48730</t>
+          <t>47314</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>19391</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41859</t>
+          <t>42386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51162</t>
+          <t>51865</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83435</t>
+          <t>84646</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59732</t>
+          <t>61236</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92829</t>
+          <t>91447</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41038</t>
+          <t>41136</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68632</t>
+          <t>68297</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>110190</t>
+          <t>108828</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>151433</t>
+          <t>151746</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -7541,12 +7541,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61411</t>
+          <t>62792</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96772</t>
+          <t>98842</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7556,12 +7556,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71837</t>
+          <t>72434</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>108174</t>
+          <t>106632</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>145378</t>
+          <t>143677</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>190595</t>
+          <t>191106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66163</t>
+          <t>64682</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>102367</t>
+          <t>98679</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>71344</t>
+          <t>73036</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>105992</t>
+          <t>107069</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7704,12 +7704,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>144810</t>
+          <t>146629</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>194819</t>
+          <t>196736</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7739,12 +7739,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28392</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45981</t>
+          <t>44275</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33898</t>
+          <t>35604</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64553</t>
+          <t>65946</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -7880,12 +7880,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7895,47 +7895,47 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>12272</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>6151</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>21445</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>12272</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>6553</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>21271</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35683</t>
+          <t>36284</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -8110,12 +8110,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12877</t>
+          <t>11840</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20580</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>38223</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>71943</t>
+          <t>72040</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42137</t>
+          <t>45140</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>64850</t>
+          <t>65345</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>104388</t>
+          <t>104506</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>72760</t>
+          <t>71668</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>111536</t>
+          <t>113783</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>63651</t>
+          <t>61953</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>99506</t>
+          <t>100425</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8386,12 +8386,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>145073</t>
+          <t>142213</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>197264</t>
+          <t>197464</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>207207</t>
+          <t>205091</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>265095</t>
+          <t>266898</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>173080</t>
+          <t>170923</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>227632</t>
+          <t>227908</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8499,12 +8499,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>391502</t>
+          <t>391059</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>473397</t>
+          <t>476298</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -8562,12 +8562,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>416406</t>
+          <t>419004</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>504199</t>
+          <t>501782</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>417625</t>
+          <t>421785</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>498070</t>
+          <t>501773</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8612,12 +8612,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>860071</t>
+          <t>858204</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>982468</t>
+          <t>977061</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -8675,12 +8675,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>924556</t>
+          <t>928945</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1026644</t>
+          <t>1031359</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8690,12 +8690,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>954520</t>
+          <t>960035</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1059493</t>
+          <t>1064618</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1910081</t>
+          <t>1906803</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2054759</t>
+          <t>2058740</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -8788,12 +8788,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>583237</t>
+          <t>577057</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>672857</t>
+          <t>673885</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>786916</t>
+          <t>789877</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>885862</t>
+          <t>893275</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1399001</t>
+          <t>1391651</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1535473</t>
+          <t>1527314</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>111464</t>
+          <t>110321</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>159066</t>
+          <t>155319</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>115196</t>
+          <t>115218</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>163134</t>
+          <t>161898</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>239339</t>
+          <t>238110</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>304557</t>
+          <t>303506</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9167,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el intervalo en el que están comprendidos los ingresos totales netos de su hogar en 2016</t>
+          <t>Población según el intervalo en el que están comprendidos los ingresos totales netos de su hogar en 2016 (tasa de respuesta: 76,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9362,82 +9362,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1886</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3323</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>823</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5479</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9475,97 +9475,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1886</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9588,12 +9588,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17657</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9736,12 +9736,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19225</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30700</t>
+          <t>28976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -9814,12 +9814,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36011</t>
+          <t>36386</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63649</t>
+          <t>61941</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31498</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59447</t>
+          <t>60995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78064</t>
+          <t>77116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115475</t>
+          <t>116591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -9927,12 +9927,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>125278</t>
+          <t>125416</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>165399</t>
+          <t>164824</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>170525</t>
+          <t>171221</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>224216</t>
+          <t>220350</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>309793</t>
+          <t>311020</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>373583</t>
+          <t>372976</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -10040,12 +10040,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>307654</t>
+          <t>311210</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>356972</t>
+          <t>357743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>400091</t>
+          <t>401890</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>457923</t>
+          <t>460776</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>727084</t>
+          <t>723250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>803147</t>
+          <t>802441</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72350</t>
+          <t>73407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108904</t>
+          <t>107293</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10168,12 +10168,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10188,12 +10188,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101631</t>
+          <t>98574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144163</t>
+          <t>142342</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>185044</t>
+          <t>186111</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>238429</t>
+          <t>239698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -10383,97 +10383,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10496,12 +10496,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10511,12 +10511,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>17929</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28654</t>
+          <t>28214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -10609,12 +10609,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>24278</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47730</t>
+          <t>48826</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10624,82 +10624,82 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>27835</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>18472</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>39761</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>62239</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>47223</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>79814</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>27835</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>18934</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>40971</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>62239</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>46605</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>80098</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -10722,12 +10722,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82175</t>
+          <t>84365</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122235</t>
+          <t>122929</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91433</t>
+          <t>92648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133411</t>
+          <t>133890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10772,47 +10772,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>213683</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>186803</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>249124</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>6,02%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>213683</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>184918</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>245419</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -10835,12 +10835,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>264095</t>
+          <t>261313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>328922</t>
+          <t>325782</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>249712</t>
+          <t>251549</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>310138</t>
+          <t>313786</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>528095</t>
+          <t>531031</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>616328</t>
+          <t>617177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10920,12 +10920,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -10948,12 +10948,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>522692</t>
+          <t>522881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>603277</t>
+          <t>603693</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>465161</t>
+          <t>466368</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>539398</t>
+          <t>538616</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10998,12 +10998,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11018,12 +11018,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1013914</t>
+          <t>1012789</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1120024</t>
+          <t>1117011</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11033,12 +11033,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -11061,12 +11061,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>393335</t>
+          <t>391739</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>467343</t>
+          <t>462918</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>403010</t>
+          <t>402354</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>475554</t>
+          <t>474161</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>818818</t>
+          <t>817727</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>915475</t>
+          <t>916206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -11174,12 +11174,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130718</t>
+          <t>133236</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179355</t>
+          <t>181408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>129495</t>
+          <t>129468</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>175257</t>
+          <t>176260</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>271423</t>
+          <t>268212</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>338462</t>
+          <t>339786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11259,12 +11259,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -11404,12 +11404,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11489,12 +11489,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -11517,12 +11517,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22476</t>
+          <t>21693</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45435</t>
+          <t>45526</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11002</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29169</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11567,12 +11567,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11587,12 +11587,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38078</t>
+          <t>37840</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>66779</t>
+          <t>67787</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11602,12 +11602,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -11630,12 +11630,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32719</t>
+          <t>32570</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58906</t>
+          <t>61357</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24701</t>
+          <t>23570</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46543</t>
+          <t>46544</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>63371</t>
+          <t>62247</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97409</t>
+          <t>97727</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11715,12 +11715,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -11743,12 +11743,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72699</t>
+          <t>74068</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106768</t>
+          <t>108816</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60363</t>
+          <t>60127</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92313</t>
+          <t>91936</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>143411</t>
+          <t>144175</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>188395</t>
+          <t>190518</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11828,12 +11828,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -11856,12 +11856,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65719</t>
+          <t>65677</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>97601</t>
+          <t>96992</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>60431</t>
+          <t>62825</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>93050</t>
+          <t>93939</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>134394</t>
+          <t>135625</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>179325</t>
+          <t>179672</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -11969,12 +11969,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>62145</t>
+          <t>62926</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>95085</t>
+          <t>95595</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11984,12 +11984,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>80157</t>
+          <t>82036</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>113934</t>
+          <t>115503</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12039,12 +12039,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>153214</t>
+          <t>152112</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>198403</t>
+          <t>198420</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>25711</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49798</t>
+          <t>48820</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>54289</t>
+          <t>52464</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12152,12 +12152,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60166</t>
+          <t>62165</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93946</t>
+          <t>95006</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -12195,12 +12195,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17028</t>
+          <t>16809</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12230,12 +12230,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>29595</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12245,12 +12245,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12265,12 +12265,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41994</t>
+          <t>40312</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12280,12 +12280,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>823</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14878</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -12538,12 +12538,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29069</t>
+          <t>29203</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>57073</t>
+          <t>57593</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12553,12 +12553,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12573,12 +12573,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17954</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40206</t>
+          <t>40101</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12588,12 +12588,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12608,12 +12608,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>53552</t>
+          <t>53720</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>88254</t>
+          <t>87290</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -12651,12 +12651,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>65986</t>
+          <t>66014</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>101746</t>
+          <t>102906</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>49310</t>
+          <t>50362</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>83030</t>
+          <t>81513</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12721,12 +12721,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>123840</t>
+          <t>121353</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>173782</t>
+          <t>172490</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -12764,12 +12764,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>172889</t>
+          <t>172448</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>228851</t>
+          <t>227097</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12799,12 +12799,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>171717</t>
+          <t>170613</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>227504</t>
+          <t>226167</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12834,12 +12834,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>359829</t>
+          <t>358648</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>439561</t>
+          <t>442238</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12849,12 +12849,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -12877,12 +12877,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>383696</t>
+          <t>386310</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>459729</t>
+          <t>464236</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12912,12 +12912,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>362801</t>
+          <t>364697</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>437952</t>
+          <t>439218</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12927,12 +12927,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12947,12 +12947,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>771297</t>
+          <t>766950</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>879016</t>
+          <t>876254</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -12990,12 +12990,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>737775</t>
+          <t>737807</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>829214</t>
+          <t>830103</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13025,12 +13025,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>750261</t>
+          <t>750440</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>848486</t>
+          <t>844067</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13060,12 +13060,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1514155</t>
+          <t>1506166</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1650755</t>
+          <t>1646390</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>752678</t>
+          <t>755352</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>852182</t>
+          <t>850604</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>856833</t>
+          <t>855126</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>957030</t>
+          <t>960320</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1637997</t>
+          <t>1639073</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1780826</t>
+          <t>1776244</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,66%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>224611</t>
+          <t>223834</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>283599</t>
+          <t>284626</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>262792</t>
+          <t>256105</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>327891</t>
+          <t>325850</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>501540</t>
+          <t>501485</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>592936</t>
+          <t>595312</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P72-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P72-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>847</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19685</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30964</t>
+          <t>31272</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30856</t>
+          <t>30636</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56370</t>
+          <t>56354</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26971</t>
+          <t>27940</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51497</t>
+          <t>51216</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64353</t>
+          <t>63853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98606</t>
+          <t>100975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108263</t>
+          <t>109569</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149485</t>
+          <t>150414</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84642</t>
+          <t>83682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>122403</t>
+          <t>120599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>203922</t>
+          <t>202734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>261295</t>
+          <t>261621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>170401</t>
+          <t>167913</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>215112</t>
+          <t>216609</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>206190</t>
+          <t>204241</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>254526</t>
+          <t>256042</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>388332</t>
+          <t>389362</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>457918</t>
+          <t>455038</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>188274</t>
+          <t>188617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>234098</t>
+          <t>235127</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1445,12 +1445,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>226380</t>
+          <t>223278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>277170</t>
+          <t>275846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>427084</t>
+          <t>427987</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>494219</t>
+          <t>493626</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32514</t>
+          <t>32831</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57527</t>
+          <t>57439</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89764</t>
+          <t>91485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76776</t>
+          <t>76190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115809</t>
+          <t>114041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,42 +1808,42 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>4727</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>13158</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>4727</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1765</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>13068</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>34588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21089</t>
+          <t>22307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25316</t>
+          <t>25730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49017</t>
+          <t>50444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25617</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51046</t>
+          <t>50277</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23734</t>
+          <t>24069</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46363</t>
+          <t>46480</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>55129</t>
+          <t>56531</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>87216</t>
+          <t>89102</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113564</t>
+          <t>113628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157670</t>
+          <t>158420</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110923</t>
+          <t>112747</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>153826</t>
+          <t>153848</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>239230</t>
+          <t>236925</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299834</t>
+          <t>300193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>267340</t>
+          <t>267851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322940</t>
+          <t>322027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192444</t>
+          <t>195634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>242832</t>
+          <t>248925</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>475005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>552583</t>
+          <t>552404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>283792</t>
+          <t>286212</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>343961</t>
+          <t>345444</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>264631</t>
+          <t>263393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>319659</t>
+          <t>320189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>563350</t>
+          <t>565103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>647515</t>
+          <t>644630</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2431,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74923</t>
+          <t>73470</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112999</t>
+          <t>112608</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81065</t>
+          <t>79555</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>119155</t>
+          <t>117175</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>165559</t>
+          <t>164982</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>220992</t>
+          <t>221169</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19956</t>
+          <t>20563</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14892</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>33105</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14822</t>
+          <t>14145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25659</t>
+          <t>25244</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50591</t>
+          <t>48570</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28085</t>
+          <t>27355</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40865</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>68978</t>
+          <t>70177</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>30017</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53361</t>
+          <t>54781</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26302</t>
+          <t>27238</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49136</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>60987</t>
+          <t>61624</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>94737</t>
+          <t>95224</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68603</t>
+          <t>67730</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101186</t>
+          <t>99134</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42150</t>
+          <t>42552</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68185</t>
+          <t>69567</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118834</t>
+          <t>116718</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>159764</t>
+          <t>158782</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62022</t>
+          <t>64348</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96820</t>
+          <t>97204</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42713</t>
+          <t>42585</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68981</t>
+          <t>68502</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>117382</t>
+          <t>115175</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>157682</t>
+          <t>156450</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -3339,12 +3339,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>35177</t>
+          <t>33903</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60845</t>
+          <t>61129</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38425</t>
+          <t>37697</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>64194</t>
+          <t>64564</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3409,12 +3409,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>77330</t>
+          <t>78864</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>114592</t>
+          <t>116625</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18814</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14064</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31754</t>
+          <t>32856</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>21304</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44671</t>
+          <t>43633</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>22633</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>47532</t>
+          <t>46819</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>79188</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22620</t>
+          <t>22317</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45512</t>
+          <t>45497</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>78620</t>
+          <t>77940</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>118330</t>
+          <t>118811</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>69105</t>
+          <t>69040</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>106374</t>
+          <t>105442</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>64417</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>102050</t>
+          <t>100052</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>141215</t>
+          <t>143988</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>192482</t>
+          <t>195029</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4134,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>232917</t>
+          <t>230844</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>292820</t>
+          <t>292056</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>197610</t>
+          <t>198060</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>254528</t>
+          <t>252017</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>446559</t>
+          <t>449055</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>527007</t>
+          <t>530680</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>468217</t>
+          <t>461883</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>540572</t>
+          <t>542118</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>344610</t>
+          <t>340957</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>411741</t>
+          <t>408979</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>827912</t>
+          <t>826400</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>931243</t>
+          <t>934445</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -4360,12 +4360,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>509644</t>
+          <t>508873</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>590979</t>
+          <t>590082</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>533264</t>
+          <t>530879</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>611559</t>
+          <t>609265</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1072023</t>
+          <t>1069102</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1181565</t>
+          <t>1180281</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -4473,12 +4473,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>284699</t>
+          <t>284600</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>348028</t>
+          <t>348628</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>331201</t>
+          <t>337275</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>404129</t>
+          <t>406717</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>631236</t>
+          <t>636312</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>727491</t>
+          <t>732588</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>27253</t>
+          <t>27560</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>53281</t>
+          <t>52722</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>72400</t>
+          <t>71879</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>107768</t>
+          <t>110914</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>105098</t>
+          <t>106725</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>151543</t>
+          <t>150554</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -5160,12 +5160,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14014</t>
+          <t>14897</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>18684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11453</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>29773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5421,12 +5421,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43754</t>
+          <t>44007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35749</t>
+          <t>35847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65164</t>
+          <t>65182</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65202</t>
+          <t>65525</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103178</t>
+          <t>101997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74860</t>
+          <t>77919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112754</t>
+          <t>114808</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151987</t>
+          <t>150932</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204493</t>
+          <t>203710</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>267818</t>
+          <t>272588</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>324377</t>
+          <t>323937</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>355228</t>
+          <t>356065</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>423972</t>
+          <t>418814</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>649383</t>
+          <t>647357</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>728769</t>
+          <t>731724</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -5725,12 +5725,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>299776</t>
+          <t>300742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>357067</t>
+          <t>357708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>466873</t>
+          <t>464715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>530565</t>
+          <t>534075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>781504</t>
+          <t>782286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>868920</t>
+          <t>871153</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45507</t>
+          <t>45244</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76427</t>
+          <t>76778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54796</t>
+          <t>54863</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86528</t>
+          <t>87942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109385</t>
+          <t>110540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153842</t>
+          <t>155700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39590</t>
+          <t>39143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14084</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22279</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47708</t>
+          <t>47143</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -6294,12 +6294,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37564</t>
+          <t>38116</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66872</t>
+          <t>71776</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32068</t>
+          <t>31190</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59543</t>
+          <t>60023</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6344,12 +6344,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>77785</t>
+          <t>77890</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>117799</t>
+          <t>120865</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -6407,12 +6407,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117688</t>
+          <t>118229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>162237</t>
+          <t>164130</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95531</t>
+          <t>94282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138850</t>
+          <t>139420</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>223562</t>
+          <t>223186</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>286950</t>
+          <t>288533</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>269779</t>
+          <t>270446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333468</t>
+          <t>334758</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>244112</t>
+          <t>245137</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>306401</t>
+          <t>306299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>531713</t>
+          <t>532574</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>618135</t>
+          <t>619542</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560059</t>
+          <t>560142</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>636333</t>
+          <t>638611</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>492125</t>
+          <t>488289</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>565075</t>
+          <t>564758</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1076894</t>
+          <t>1063558</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1181240</t>
+          <t>1178436</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>249764</t>
+          <t>252176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>311842</t>
+          <t>312657</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>274280</t>
+          <t>274308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>340758</t>
+          <t>339969</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>543055</t>
+          <t>544201</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>628899</t>
+          <t>632261</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -6859,12 +6859,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47417</t>
+          <t>45437</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80211</t>
+          <t>76896</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40143</t>
+          <t>40967</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72585</t>
+          <t>72852</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92770</t>
+          <t>95230</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>140030</t>
+          <t>138240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10517</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -7202,12 +7202,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35958</t>
+          <t>35642</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>12366</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33169</t>
+          <t>31677</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31834</t>
+          <t>30915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>59994</t>
+          <t>59518</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -7315,12 +7315,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>25279</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47314</t>
+          <t>48222</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42386</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51865</t>
+          <t>49444</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>84646</t>
+          <t>82923</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61236</t>
+          <t>60397</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>91447</t>
+          <t>91553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41136</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68297</t>
+          <t>68459</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>108828</t>
+          <t>108998</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>151746</t>
+          <t>153487</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -7541,12 +7541,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62792</t>
+          <t>62942</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>98842</t>
+          <t>96432</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7556,12 +7556,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>72434</t>
+          <t>71848</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>106632</t>
+          <t>105354</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>143677</t>
+          <t>144451</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>191106</t>
+          <t>190656</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>64682</t>
+          <t>65608</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>98679</t>
+          <t>98111</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>73036</t>
+          <t>71299</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>107069</t>
+          <t>105761</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7704,12 +7704,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>146629</t>
+          <t>146457</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>196736</t>
+          <t>194687</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7739,12 +7739,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28149</t>
+          <t>28949</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>21380</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44275</t>
+          <t>45413</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>35799</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>65946</t>
+          <t>65149</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -7880,12 +7880,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20209</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21445</t>
+          <t>22510</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36284</t>
+          <t>36571</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -8110,12 +8110,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11840</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19197</t>
+          <t>18250</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>38223</t>
+          <t>38307</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>72040</t>
+          <t>69502</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45140</t>
+          <t>41917</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65345</t>
+          <t>64911</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>104506</t>
+          <t>104548</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>71668</t>
+          <t>70589</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>113783</t>
+          <t>109981</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>61953</t>
+          <t>62864</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>100425</t>
+          <t>101285</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8386,12 +8386,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>142213</t>
+          <t>144323</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>197464</t>
+          <t>201130</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -8449,12 +8449,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>205091</t>
+          <t>202832</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>266898</t>
+          <t>264603</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>170923</t>
+          <t>170944</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>227908</t>
+          <t>229137</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>391059</t>
+          <t>393039</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>476298</t>
+          <t>477771</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -8562,12 +8562,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>419004</t>
+          <t>420211</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>501782</t>
+          <t>503270</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>421785</t>
+          <t>420079</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>501773</t>
+          <t>498345</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8612,12 +8612,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>858204</t>
+          <t>859170</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>977061</t>
+          <t>973359</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -8675,12 +8675,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>928945</t>
+          <t>927323</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1031359</t>
+          <t>1026765</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8690,12 +8690,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>960035</t>
+          <t>953726</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1064618</t>
+          <t>1061062</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1906803</t>
+          <t>1904912</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2058740</t>
+          <t>2051810</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -8788,12 +8788,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>577057</t>
+          <t>576421</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>673885</t>
+          <t>666274</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>789877</t>
+          <t>792561</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>893275</t>
+          <t>889929</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1391651</t>
+          <t>1399488</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1527314</t>
+          <t>1532652</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>110321</t>
+          <t>112028</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>155319</t>
+          <t>158121</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>115218</t>
+          <t>115173</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>161898</t>
+          <t>163258</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>238110</t>
+          <t>238244</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>303506</t>
+          <t>304760</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>13213</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -9701,12 +9701,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9736,12 +9736,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28976</t>
+          <t>29621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -9814,12 +9814,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>37214</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61941</t>
+          <t>64237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32551</t>
+          <t>33596</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60995</t>
+          <t>61198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77116</t>
+          <t>75579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116591</t>
+          <t>112944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -9927,12 +9927,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>125416</t>
+          <t>122191</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>164824</t>
+          <t>164044</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>171221</t>
+          <t>174202</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220350</t>
+          <t>224316</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>311020</t>
+          <t>308244</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>372976</t>
+          <t>375391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -10040,12 +10040,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>311210</t>
+          <t>309110</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>357743</t>
+          <t>358964</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>401890</t>
+          <t>400801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>460776</t>
+          <t>460076</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>723250</t>
+          <t>722912</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>802441</t>
+          <t>803644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73407</t>
+          <t>72748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107293</t>
+          <t>109639</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10168,12 +10168,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10188,12 +10188,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98574</t>
+          <t>101643</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142342</t>
+          <t>142218</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>186111</t>
+          <t>183587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>239698</t>
+          <t>236714</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -10496,12 +10496,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10511,12 +10511,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28214</t>
+          <t>27188</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -10609,12 +10609,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24278</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48826</t>
+          <t>46579</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39761</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>47223</t>
+          <t>48203</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>79814</t>
+          <t>80802</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -10722,12 +10722,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84365</t>
+          <t>83687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122929</t>
+          <t>126689</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92648</t>
+          <t>92835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133890</t>
+          <t>137115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>186803</t>
+          <t>187130</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>249124</t>
+          <t>242625</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10807,12 +10807,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -10835,12 +10835,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>261313</t>
+          <t>262800</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>325782</t>
+          <t>325504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>251549</t>
+          <t>252059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>313786</t>
+          <t>310542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>531031</t>
+          <t>531621</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>617177</t>
+          <t>619657</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10920,12 +10920,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -10948,12 +10948,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>522881</t>
+          <t>524657</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>603693</t>
+          <t>600789</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>466368</t>
+          <t>465025</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>538616</t>
+          <t>537719</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10998,12 +10998,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11018,12 +11018,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1012789</t>
+          <t>1006854</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1117011</t>
+          <t>1117285</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>391739</t>
+          <t>393971</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>462918</t>
+          <t>464919</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>402354</t>
+          <t>405377</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>474161</t>
+          <t>474053</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>817727</t>
+          <t>816782</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>916206</t>
+          <t>916564</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -11174,12 +11174,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133236</t>
+          <t>131075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181408</t>
+          <t>179917</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>129468</t>
+          <t>129595</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>176260</t>
+          <t>177216</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>268212</t>
+          <t>274900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>339786</t>
+          <t>343436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11259,12 +11259,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -11404,12 +11404,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11242</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -11517,12 +11517,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45526</t>
+          <t>45729</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>28216</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11567,12 +11567,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11587,12 +11587,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37840</t>
+          <t>38582</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>67787</t>
+          <t>67713</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11602,12 +11602,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -11630,12 +11630,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32570</t>
+          <t>32098</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>61357</t>
+          <t>59613</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23570</t>
+          <t>24143</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46544</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11680,12 +11680,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>62247</t>
+          <t>61562</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97727</t>
+          <t>96296</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11715,12 +11715,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -11743,12 +11743,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74068</t>
+          <t>73844</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>108816</t>
+          <t>108656</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60127</t>
+          <t>60694</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91936</t>
+          <t>92789</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>144175</t>
+          <t>143260</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>190518</t>
+          <t>192113</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11828,12 +11828,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -11856,12 +11856,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65677</t>
+          <t>64435</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96992</t>
+          <t>96950</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62825</t>
+          <t>62163</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>93939</t>
+          <t>93327</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>135625</t>
+          <t>135316</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>179672</t>
+          <t>181047</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -11969,12 +11969,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>62926</t>
+          <t>63778</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>95595</t>
+          <t>95609</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>82036</t>
+          <t>82419</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>115503</t>
+          <t>115367</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12039,12 +12039,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>152112</t>
+          <t>152316</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>198420</t>
+          <t>200872</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12054,12 +12054,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -12082,12 +12082,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25711</t>
+          <t>25680</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48820</t>
+          <t>50146</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29753</t>
+          <t>28628</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52464</t>
+          <t>53266</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12152,12 +12152,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62165</t>
+          <t>60781</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>95006</t>
+          <t>94307</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -12195,12 +12195,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16809</t>
+          <t>16512</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12230,12 +12230,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11720</t>
+          <t>11707</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29595</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12245,12 +12245,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12265,12 +12265,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>18936</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>40312</t>
+          <t>39629</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12280,12 +12280,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10944</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>15290</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -12538,12 +12538,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29203</t>
+          <t>29701</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>57593</t>
+          <t>54506</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12553,12 +12553,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12573,12 +12573,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>16938</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40101</t>
+          <t>39383</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12588,12 +12588,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12608,12 +12608,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>53720</t>
+          <t>53587</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>87290</t>
+          <t>86920</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>66014</t>
+          <t>65799</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>102906</t>
+          <t>104578</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>50362</t>
+          <t>49778</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>81513</t>
+          <t>82509</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12721,12 +12721,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>121353</t>
+          <t>124025</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>172490</t>
+          <t>174241</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -12764,12 +12764,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>172448</t>
+          <t>172389</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>227097</t>
+          <t>228108</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12799,12 +12799,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>170613</t>
+          <t>171294</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>226167</t>
+          <t>225957</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12834,12 +12834,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>358648</t>
+          <t>362408</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>442238</t>
+          <t>442399</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>386310</t>
+          <t>384039</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>464236</t>
+          <t>462762</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12912,12 +12912,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>364697</t>
+          <t>365353</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>439218</t>
+          <t>441540</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12927,12 +12927,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12947,12 +12947,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>766950</t>
+          <t>770352</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>876254</t>
+          <t>877354</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -12990,12 +12990,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>737807</t>
+          <t>730301</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>830103</t>
+          <t>826419</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13025,12 +13025,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>750440</t>
+          <t>747730</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>844067</t>
+          <t>841700</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13040,12 +13040,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13060,12 +13060,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1506166</t>
+          <t>1507518</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1646390</t>
+          <t>1644391</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>755352</t>
+          <t>757801</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>850604</t>
+          <t>852239</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>855126</t>
+          <t>859411</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>960320</t>
+          <t>958399</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1639073</t>
+          <t>1639131</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1776244</t>
+          <t>1777044</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>223834</t>
+          <t>224584</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>284626</t>
+          <t>284441</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>256105</t>
+          <t>261218</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>325850</t>
+          <t>328711</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13266,47 +13266,47 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>544579</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>502363</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>586670</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
           <t>9,52%</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>544579</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>501485</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>595312</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>9,5%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
